--- a/02_加值成品/生物/生物8-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物8-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物8-1 族群與群集　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物8-1 族群與群集　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>同區域同種生物的總和是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>族群</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>多種</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>掠食</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>調節數量</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>同種</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>同區域所有族群的集合是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>調節數量</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>寄生</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>掠食</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>群集</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>多種</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>爭奪資源的關係是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>掠食</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>族群</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>寄生</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>競爭</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>爭奪</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>捕食與被捕食的關係是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>同種</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>掠食</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>多種</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>食物天敵環境</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>捕食</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>兩生物緊密生活在一起是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>共生</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>交互作用</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>群集</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>同種</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>共生</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>一方得利一方受害是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>掠食</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>競爭</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>寄生</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>調節數量</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>寄生</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>族群是同種還異種？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>共生</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>互利共生</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>族群</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>同種</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>單一物種</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>群集包含幾種生物？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>多種</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>食物天敵環境</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>掠食</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>寄生</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>多物種</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>同一區域不同物種族群的集合是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>群集</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>寄生</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>競爭</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>掠食</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>群集</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>蜜蜂採花蜜同時助授粉屬？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>群集</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>互利共生</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>食物天敵環境</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>競爭</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>互利</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物8-1 族群與群集　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物8-1 族群與群集　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>小丑魚與海葵屬哪種關係？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>共生</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>掠食</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>食物天敵環境</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>互利共生</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>互利</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>獅子捕食羚羊屬？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>調節數量</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>共生</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>寄生</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>掠食</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>捕食</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>兩植物爭陽光屬？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>競爭</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>寄生</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>群集</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>多種</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>爭資源</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>跳蚤吸血屬？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>共生</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>寄生</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>族群</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>競爭</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>寄生</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>族群數量受什麼影響？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>同種</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>群集</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>食物天敵環境</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>多種</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>因素</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>群集組成受什麼影響？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>掠食</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>族群</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>競爭</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>交互作用</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>關係</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>掠食對被捕食族群的作用？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>互利共生</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>競爭</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>共生</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>調節數量</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>平衡</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>族群密度指？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>大量繁殖破壞平衡</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>彼此獲益提高生存</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>單位面積個體數</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>決定物種能否共存與數量</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>密度</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>菟絲子吸取宿主養分屬？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>族群</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>寄生</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>競爭</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>群集</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>寄生</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>食物與空間有限時同種個體會？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>共生</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>交互作用</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>競爭</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>群集</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>競爭</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物8-1 族群與群集　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物8-1 族群與群集　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>比較族群與群集的差別？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>族群同種、群集含多種族群</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>競爭掠食共生寄生各舉例</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>資源有限使競爭者分化或減少</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>寄生長期依附宿主、掠食直接捕食</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>區別</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>說明四種生物交互作用並舉例？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>競爭掠食共生寄生各舉例</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>單位面積個體數</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>大量繁殖破壞平衡</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>調節被捕食者數量避免過度增長</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>類型</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>掠食關係如何維持生態平衡？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>寄生長期依附宿主、掠食直接捕食</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>競爭掠食共生寄生各舉例</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>調節被捕食者數量避免過度增長</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>單位面積個體數</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>平衡</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>互利共生對雙方的意義？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>寄生長期依附宿主、掠食直接捕食</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>調節被捕食者數量避免過度增長</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>族群同種、群集含多種族群</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>彼此獲益提高生存</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>共生</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>競爭如何影響族群分布？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>大量繁殖破壞平衡</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>族群同種、群集含多種族群</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>競爭掠食共生寄生各舉例</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>資源有限使競爭者分化或減少</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>競爭</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>交互作用如何塑造群集組成？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>決定物種能否共存與數量</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>單位面積個體數</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>調節被捕食者數量避免過度增長</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>大量繁殖破壞平衡</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>塑造</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>寄生與掠食的差別？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>調節被捕食者數量避免過度增長</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>寄生長期依附宿主、掠食直接捕食</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>寄生一方受害互利雙方得利</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>決定物種能否共存與數量</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>族群數量過度增加可能造成？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>寄生一方受害互利雙方得利</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>族群同種、群集含多種族群</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>資源耗竭與競爭加劇</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>寄生長期依附宿主、掠食直接捕食</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>後果</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>引入缺乏天敵的外來種可能造成？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>大量繁殖破壞平衡</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>決定物種能否共存與數量</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>彼此獲益提高生存</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>單位面積個體數</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>入侵</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>寄生與互利共生的差別？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>彼此獲益提高生存</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>大量繁殖破壞平衡</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>調節被捕食者數量避免過度增長</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>寄生一方受害互利雙方得利</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>區別</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物8-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物8-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>同種</t>
+          <t>同種生物：在同一個地方生活的同一種生物全部加起來，就稱為一個族群</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>多種</t>
+          <t>多種族群：把同一地區裡所有不同種的族群通通算在一起，就叫做群集</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>爭奪</t>
+          <t>爭奪資源：兩種生物搶著要同樣的食物、空間或陽光，這種關係叫做競爭</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>捕食</t>
+          <t>捕食關係：一種生物捕食另一種生物來獲取食物，這種關係叫做掠食</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>共生</t>
+          <t>共同生活：兩種生物長期生活在一起並互相影響，這種關係叫做共生</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>寄生</t>
+          <t>片面得利：一方靠依附另一方獲得好處，卻讓對方受害，這種關係叫做寄生</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>單一物種</t>
+          <t>單一物種：族群指的是同一個地區裡同一種生物聚集在一起，不包含別種生物</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>多物種</t>
+          <t>多種生物：群集是同一地區裡所有不同物種族群加起來，所以包含很多種生物</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>群集</t>
+          <t>群集：在同一個區域內，各種不同物種的族群共同生活組成的整體，稱為群集</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>互利</t>
+          <t>互利：蜜蜂採花蜜獲得食物，同時幫花朵傳播花粉，雙方都獲得好處，屬於互利共生的關係</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>互利</t>
+          <t>互相得利：小丑魚靠海葵保護、海葵靠小丑魚清潔驅敵，雙方都得到好處，屬互利共生</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>捕食</t>
+          <t>捕食關係：獅子直接獵捕羚羊當作食物，這種一方吃掉另一方的關係就是掠食</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>爭資源</t>
+          <t>爭奪資源：兩株植物同時需要陽光才能生長，彼此搶奪陽光就是一種競爭</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>寄生</t>
+          <t>依附宿主：跳蚤附著在動物身上吸血維生，讓宿主受害，這種關係屬於寄生</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>因素</t>
+          <t>多重因素：食物多寡、天敵數量與環境好壞都會讓族群的個體數量增加或減少</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>關係</t>
+          <t>彼此牽動：物種間的競爭、掠食、共生等交互作用，會決定群集裡有哪些生物能生存</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>控制數量：掠食者吃掉一部分獵物，能避免被捕食者數量增加過多，維持生態平衡</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>密度</t>
+          <t>平均分布：族群密度是指在一定面積或體積內，平均有多少個體存在的數量</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>寄生</t>
+          <t>寄生：菟絲子纏繞在其他植物上，吸取宿主的養分維生，對宿主有害，自己卻得利，這種關係稱為寄生</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>競爭</t>
+          <t>競爭：當食物、空間等資源有限時，同一族群內的個體會互相競爭這些有限的資源</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>範圍不同：族群只包含同一地區的同一種生物，群集則是把當地所有不同族群都算進去</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>類型</t>
+          <t>四種類型：生物間常見的關係有競爭（搶資源）、掠食（捕食）、共生（互利）和寄生（依附）</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>互相牽制：掠食者持續捕食獵物，讓被捕食者的數量不會無限增加，維持生態系統的穩定</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>共生</t>
+          <t>雙贏合作：互利共生的兩種生物互相提供好處，讓彼此更容易存活下去</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>競爭</t>
+          <t>資源有限：當資源不夠兩種生物共用時，競爭較弱的一方數量會減少或被迫遷移他處</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>塑造</t>
+          <t>相互影響：競爭、掠食等交互作用會決定哪些物種能一起生存，以及各自數量的多寡</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>方式不同：寄生是長期依附在宿主身上慢慢獲取養分，掠食則是直接捕捉並吃掉獵物</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>後果</t>
+          <t>資源不足：當族群數量增加太多，食物與空間會不夠用，導致同類間的競爭變得更激烈</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>入侵</t>
+          <t>入侵：外來種若在新環境中沒有天敵制衡，可能大量繁殖，與原生物種競爭資源，破壞當地原本的生態平衡</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>區別：寄生關係中一方（宿主）會受到傷害，另一方（寄生者）得利;互利共生則是雙方都能從關係中獲得好處，兩者對彼此的影響不同</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物8-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物8-1_三種難度測驗卷.xlsx
@@ -728,17 +728,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>交互作用</t>
+          <t>同種</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>群集</t>
+          <t>競爭</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>同種</t>
+          <t>寄生</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>食物天敵環境</t>
+          <t>交互作用</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>競爭</t>
+          <t>寄生</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>共生</t>
+          <t>群集</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>食物天敵環境</t>
+          <t>競爭</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
